--- a/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 34,12</t>
+          <t>23,96; 33,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 39,4</t>
+          <t>30,82; 38,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,96; 35,52</t>
+          <t>28,87; 35,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,42</t>
+          <t>3,51; 10,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,02</t>
+          <t>3,78; 9,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,23</t>
+          <t>4,92; 9,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,59</t>
+          <t>2,9; 6,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,8</t>
+          <t>3,14; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,09</t>
+          <t>3,44; 5,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,98</t>
+          <t>6,2; 12,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,96</t>
+          <t>7,49; 13,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,06</t>
+          <t>7,93; 12,06</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57073; 81500</t>
+          <t>57230; 79547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83464; 108062</t>
+          <t>84545; 106919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148611; 182282</t>
+          <t>148141; 180937</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46873; 122161</t>
+          <t>41197; 121227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39479; 96656</t>
+          <t>40551; 97032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112739; 207106</t>
+          <t>110397; 205944</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10184; 22863</t>
+          <t>10063; 23368</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9989; 21747</t>
+          <t>10032; 22212</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22386; 40615</t>
+          <t>22938; 39934</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>108810; 210534</t>
+          <t>108972; 212476</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>116250; 215928</t>
+          <t>124717; 218387</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>266177; 413061</t>
+          <t>271515; 412870</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,96; 33,31</t>
+          <t>23,37; 33,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,82; 38,98</t>
+          <t>30,85; 39,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 35,26</t>
+          <t>28,74; 35,26</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,34</t>
+          <t>7,7; 11,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,05</t>
+          <t>7,0; 9,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,18</t>
+          <t>7,69; 9,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,74</t>
+          <t>2,91; 6,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,95</t>
+          <t>2,88; 6,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,99</t>
+          <t>3,21; 5,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,09</t>
+          <t>9,92; 12,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,11</t>
+          <t>11,07; 13,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,06</t>
+          <t>10,88; 12,84</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>73838</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95109</t>
+          <t>105047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163288</t>
+          <t>178885</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57230; 79547</t>
+          <t>61866; 87562</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84545; 106919</t>
+          <t>92531; 118085</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148141; 180937</t>
+          <t>162291; 199096</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90656</t>
+          <t>95776</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72564</t>
+          <t>79075</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>174851</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41197; 121227</t>
+          <t>77763; 113574</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40551; 97032</t>
+          <t>67046; 94559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110397; 205944</t>
+          <t>151288; 195633</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>16049</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>32861</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10063; 23368</t>
+          <t>11133; 24786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10032; 22212</t>
+          <t>10347; 22940</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22938; 39934</t>
+          <t>23786; 42506</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186426</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>182690</t>
+          <t>200171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357061</t>
+          <t>386597</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>108972; 212476</t>
+          <t>164551; 209289</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124717; 218387</t>
+          <t>179024; 221068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>271515; 412870</t>
+          <t>356316; 420388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
